--- a/suite_test_pec_mobile.xlsx
+++ b/suite_test_pec_mobile.xlsx
@@ -1219,10 +1219,10 @@
           <t>1. Accedere con credenziali valide su viewport mobile.
 2. Attendere il caricamento della webmail.
 3. Verificare che l'URL contenga 'INBOX', 'messages' o 'mail'.
-4. Verificare la visibilità della bottom navigation bar.
-5. Verificare la presenza del bottone hamburger (≡) nell'header.
-6. Verificare la presenza di un'intestazione di sezione (h1 o equivalente).
-7. Scattare screenshot.</t>
+4. Scattare screenshot.
+5. Verificare la visibilità della bottom navigation bar (assert).
+6. Verificare la presenza del bottone hamburger (≡) nell'header (assert).
+7. Verificare la presenza di un'intestazione di sezione (h1 o equivalente, assert).</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
@@ -1261,8 +1261,8 @@
 2. Cliccare il tab 'Calendario' nella bottom navigation bar.
 3. Attendere il caricamento della sezione.
 4. Verificare che l'URL contenga 'calendar'/'calendario' oppure che l'heading 'Calendario' sia visibile.
-5. Verificare la presenza di elementi calendario (griglia, controlli, pulsante 'Nuovo evento').
-6. Scattare screenshot.</t>
+5. Scattare screenshot.
+6. Verificare la presenza di elementi calendario (griglia, controlli, pulsante 'Nuovo evento', assert).</t>
         </is>
       </c>
       <c r="G4" s="31" t="inlineStr">
@@ -1305,9 +1305,9 @@
 6. Inserire un titolo univoco (con timestamp).
 7. Cliccare 'Salva'.
 8. Scattare screenshot post-salvataggio.
-9. Verificare che NON appaia un toast di errore.
-10. Cleanup: eliminare l'evento dalla vista Eventi.
-11. Scattare screenshot finale.</t>
+9. Verificare che NON appaia un toast di errore (assert).
+10. Scattare screenshot finale.
+11. Cleanup: eliminare l'evento dalla vista Eventi.</t>
         </is>
       </c>
       <c r="G5" s="37" t="inlineStr">
@@ -1346,8 +1346,8 @@
 2. Cliccare il tab 'Contatti' nella bottom navigation bar.
 3. Attendere il caricamento della sezione.
 4. Verificare che l'URL contenga 'contacts'/'contatti' oppure che l'heading 'Contatti' sia visibile.
-5. Verificare la presenza di un campo ricerca o lista contatti.
-6. Scattare screenshot.</t>
+5. Scattare screenshot.
+6. Verificare la presenza di un campo ricerca o lista contatti (assert).</t>
         </is>
       </c>
       <c r="G6" s="43" t="inlineStr">
@@ -1391,8 +1391,8 @@
 7. Aprire la barra di ricerca e cercare il nome del contatto.
 8. Verificare che il contatto sia trovato (via testo o frame-record-desktop).
 9. Scattare screenshot del risultato.
-10. Cleanup: selezionare e eliminare il contatto.
-11. Scattare screenshot finale.</t>
+10. Scattare screenshot finale.
+11. Cleanup: selezionare e eliminare il contatto.</t>
         </is>
       </c>
       <c r="G7" s="37" t="inlineStr">
@@ -1435,8 +1435,8 @@
 6. Verificare la presenza delle voci 'In arrivo' e 'Inviati' nel drawer.
 7. Cliccare 'Inviati' e verificare navigazione.
 8. Tornare all'inbox via bottom tab 'Messaggi'.
-9. Verificare che l'URL sia relativo all'inbox (INBOX o messages).
-10. Scattare screenshot finale.</t>
+9. Scattare screenshot finale.
+10. Verificare che l'URL sia relativo all'inbox (INBOX o messages, assert).</t>
         </is>
       </c>
       <c r="G8" s="50" t="inlineStr">
@@ -1478,8 +1478,8 @@
 5. Fallback: click alle coordinate centro-alto del viewport.
 6. Attendere il caricamento del dettaglio.
 7. Scattare screenshot del dettaglio.
-8. Verificare che l'URL contenga 'webmail'.
-9. Scattare screenshot finale.</t>
+8. Scattare screenshot finale.
+9. Verificare che l'URL contenga 'webmail' (assert).</t>
         </is>
       </c>
       <c r="G9" s="37" t="inlineStr">
@@ -1521,8 +1521,8 @@
 5. Scattare screenshot del form compilato.
 6. Cliccare 'Invia'.
 7. Attendere 3 secondi.
-8. Verificare la presenza del toast di conferma (aru-toast__message).
-9. Scattare screenshot finale.</t>
+8. Scattare screenshot finale.
+9. Verificare la presenza del toast di conferma (aru-toast__message, assert).</t>
         </is>
       </c>
       <c r="G10" s="50" t="inlineStr">
@@ -1564,8 +1564,8 @@
 5. Scattare screenshot della pagina impostazioni.
 6. Attendere il caricamento Angular.
 7. Verificare settings_reached (URL o impostazioni nel titolo).
-8. Verificare il contenuto (h1 Impostazioni, sezioni Casella PEC, ecc.).
-9. Scattare screenshot finale.</t>
+8. Scattare screenshot finale.
+9. Verificare il contenuto (h1 Impostazioni, sezioni Casella PEC, ecc., assert).</t>
         </is>
       </c>
       <c r="G11" s="57" t="inlineStr">
@@ -1607,8 +1607,8 @@
 5. Verificare la presenza di almeno 2 sezioni tra: Casella PEC, Messaggi e scrittura, Account e sicurezza, Aspetto.
 6. Cliccare 'Casella PEC' per verificare la navigazione interna.
 7. Scattare screenshot.
-8. Verificare che almeno 2 sezioni su 4 siano trovate.
-9. Scattare screenshot finale.</t>
+8. Scattare screenshot finale.
+9. Verificare che almeno 2 sezioni su 4 siano trovate (assert).</t>
         </is>
       </c>
       <c r="G12" s="37" t="inlineStr">
@@ -1701,10 +1701,10 @@
           <t>1. Accedere con credenziali valide su viewport mobile.
 2. Attendere il caricamento della webmail.
 3. Verificare che l'URL contenga 'INBOX', 'messages' o 'mail'.
-4. Verificare la visibilità della bottom navigation bar.
-5. Verificare la presenza del bottone hamburger (≡) nell'header.
-6. Verificare la presenza di un'intestazione di sezione (h1 o equivalente).
-7. Scattare screenshot.</t>
+4. Scattare screenshot.
+5. Verificare la visibilità della bottom navigation bar (assert).
+6. Verificare la presenza del bottone hamburger (≡) nell'header (assert).
+7. Verificare la presenza di un'intestazione di sezione (h1 o equivalente, assert).</t>
         </is>
       </c>
       <c r="E3" s="25" t="inlineStr">
@@ -1799,8 +1799,8 @@
 2. Cliccare il tab 'Calendario' nella bottom navigation bar.
 3. Attendere il caricamento della sezione.
 4. Verificare che l'URL contenga 'calendar'/'calendario' oppure che l'heading 'Calendario' sia visibile.
-5. Verificare la presenza di elementi calendario (griglia, controlli, pulsante 'Nuovo evento').
-6. Scattare screenshot.</t>
+5. Scattare screenshot.
+6. Verificare la presenza di elementi calendario (griglia, controlli, pulsante 'Nuovo evento', assert).</t>
         </is>
       </c>
       <c r="E3" s="31" t="inlineStr">
@@ -1835,9 +1835,9 @@
 6. Inserire un titolo univoco (con timestamp).
 7. Cliccare 'Salva'.
 8. Scattare screenshot post-salvataggio.
-9. Verificare che NON appaia un toast di errore.
-10. Cleanup: eliminare l'evento dalla vista Eventi.
-11. Scattare screenshot finale.</t>
+9. Verificare che NON appaia un toast di errore (assert).
+10. Scattare screenshot finale.
+11. Cleanup: eliminare l'evento dalla vista Eventi.</t>
         </is>
       </c>
       <c r="E4" s="37" t="inlineStr">
@@ -1932,8 +1932,8 @@
 2. Cliccare il tab 'Contatti' nella bottom navigation bar.
 3. Attendere il caricamento della sezione.
 4. Verificare che l'URL contenga 'contacts'/'contatti' oppure che l'heading 'Contatti' sia visibile.
-5. Verificare la presenza di un campo ricerca o lista contatti.
-6. Scattare screenshot.</t>
+5. Scattare screenshot.
+6. Verificare la presenza di un campo ricerca o lista contatti (assert).</t>
         </is>
       </c>
       <c r="E3" s="43" t="inlineStr">
@@ -1969,8 +1969,8 @@
 7. Aprire la barra di ricerca e cercare il nome del contatto.
 8. Verificare che il contatto sia trovato (via testo o frame-record-desktop).
 9. Scattare screenshot del risultato.
-10. Cleanup: selezionare e eliminare il contatto.
-11. Scattare screenshot finale.</t>
+10. Scattare screenshot finale.
+11. Cleanup: selezionare e eliminare il contatto.</t>
         </is>
       </c>
       <c r="E4" s="37" t="inlineStr">
@@ -2069,8 +2069,8 @@
 6. Verificare la presenza delle voci 'In arrivo' e 'Inviati' nel drawer.
 7. Cliccare 'Inviati' e verificare navigazione.
 8. Tornare all'inbox via bottom tab 'Messaggi'.
-9. Verificare che l'URL sia relativo all'inbox (INBOX o messages).
-10. Scattare screenshot finale.</t>
+9. Scattare screenshot finale.
+10. Verificare che l'URL sia relativo all'inbox (INBOX o messages, assert).</t>
         </is>
       </c>
       <c r="E3" s="50" t="inlineStr">
@@ -2104,8 +2104,8 @@
 5. Fallback: click alle coordinate centro-alto del viewport.
 6. Attendere il caricamento del dettaglio.
 7. Scattare screenshot del dettaglio.
-8. Verificare che l'URL contenga 'webmail'.
-9. Scattare screenshot finale.</t>
+8. Scattare screenshot finale.
+9. Verificare che l'URL contenga 'webmail' (assert).</t>
         </is>
       </c>
       <c r="E4" s="37" t="inlineStr">
@@ -2139,8 +2139,8 @@
 5. Scattare screenshot del form compilato.
 6. Cliccare 'Invia'.
 7. Attendere 3 secondi.
-8. Verificare la presenza del toast di conferma (aru-toast__message).
-9. Scattare screenshot finale.</t>
+8. Scattare screenshot finale.
+9. Verificare la presenza del toast di conferma (aru-toast__message, assert).</t>
         </is>
       </c>
       <c r="E5" s="50" t="inlineStr">
@@ -2238,8 +2238,8 @@
 5. Scattare screenshot della pagina impostazioni.
 6. Attendere il caricamento Angular.
 7. Verificare settings_reached (URL o impostazioni nel titolo).
-8. Verificare il contenuto (h1 Impostazioni, sezioni Casella PEC, ecc.).
-9. Scattare screenshot finale.</t>
+8. Scattare screenshot finale.
+9. Verificare il contenuto (h1 Impostazioni, sezioni Casella PEC, ecc., assert).</t>
         </is>
       </c>
       <c r="E3" s="57" t="inlineStr">
@@ -2273,8 +2273,8 @@
 5. Verificare la presenza di almeno 2 sezioni tra: Casella PEC, Messaggi e scrittura, Account e sicurezza, Aspetto.
 6. Cliccare 'Casella PEC' per verificare la navigazione interna.
 7. Scattare screenshot.
-8. Verificare che almeno 2 sezioni su 4 siano trovate.
-9. Scattare screenshot finale.</t>
+8. Scattare screenshot finale.
+9. Verificare che almeno 2 sezioni su 4 siano trovate (assert).</t>
         </is>
       </c>
       <c r="E4" s="37" t="inlineStr">
